--- a/etf_holdings/2026-08-25_common_holdings_all_00981A_00991A_00980A_00982A_00403A_00985A_00992A_00990A.xlsx
+++ b/etf_holdings/2026-08-25_common_holdings_all_00981A_00991A_00980A_00982A_00403A_00985A_00992A_00990A.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.12%</t>
+          <t>10.09%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -602,7 +602,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12.72%</t>
+          <t>12.71%</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9.18%</t>
+          <t>9.14%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -628,7 +628,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8.74%</t>
+          <t>8.67%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17.19%</t>
+          <t>17.14%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13.98%</t>
+          <t>13.92%</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -667,7 +667,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>7.47%</t>
+          <t>7.40%</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -688,12 +688,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>81.67%</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>10.25%</t>
+          <t>10.21%</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.43%</t>
+          <t>9.59%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -736,7 +736,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.05%</t>
+          <t>9.22%</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -762,11 +762,11 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>320000</v>
+        <v>322000</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>5.63%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -788,7 +788,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -822,12 +822,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>42.05%</t>
+          <t>42.42%</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.30%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.39%</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4.77%</t>
+          <t>4.79%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6.73%</t>
+          <t>6.56%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>4.69%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>33.43%</t>
+          <t>32.89%</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.87%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.15%</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>25.71%</t>
+          <t>25.13%</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1107,12 +1107,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1120,116 +1120,112 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>3.95%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>19479000</v>
+        <v>9624000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>南亞電路</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>9000</v>
+        <v>3250000</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>南亞電路板</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>526000</v>
+        <v>203000</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1.16%</t>
-        </is>
-      </c>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>959000</v>
+        <v>1000</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>8000000</v>
+        <v>2640000</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>南亞電路板</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>335000</v>
+        <v>48000</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>716000</v>
+        <v>300000</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>641000</v>
+        <v>302000</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13.69%</t>
+          <t>13.66%</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1241,12 +1237,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1254,107 +1250,107 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9624000</v>
+        <v>19479000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>南亞電路</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.39%</t>
-        </is>
-      </c>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>3250000</v>
+        <v>9000</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>南亞電路板</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>203000</v>
+        <v>526000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
+      </c>
       <c r="O7" t="n">
-        <v>1000</v>
+        <v>965000</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>2640000</v>
+        <v>8000000</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>南亞電路板</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>48000</v>
+        <v>335000</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>300000</v>
+        <v>716000</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>302000</v>
+        <v>641000</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13.56%</t>
+          <t>13.60%</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
